--- a/exports/AUBANK_full_report.xlsx
+++ b/exports/AUBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>659.5</v>
+        <v>636</v>
       </c>
       <c r="I2" t="n">
         <v>646.5023079450569</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K2" t="n">
-        <v>7.06</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
         <v>2.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>2.18</v>
       </c>
       <c r="N2" t="n">
-        <v>4.18</v>
+        <v>5.38</v>
       </c>
       <c r="O2" t="n">
         <v>1.11</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44631.38541666666</v>
+        <v>44631.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>585.85</v>
+        <v>596</v>
       </c>
       <c r="I3" t="n">
         <v>589.8109606877099</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>7.89</v>
+        <v>6.29</v>
       </c>
       <c r="L3" t="n">
         <v>3.54</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.78</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44685.38541666666</v>
+        <v>44685.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>690.6</v>
+        <v>665.95</v>
       </c>
       <c r="I4" t="n">
         <v>673.1756055509545</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>53.83333333333334</v>
+        <v>54</v>
       </c>
       <c r="K4" t="n">
-        <v>15.87</v>
+        <v>11.74</v>
       </c>
       <c r="L4" t="n">
         <v>9.720000000000001</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44701.55208333334</v>
+        <v>44704.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>655.05</v>
+        <v>675.6</v>
       </c>
       <c r="I5" t="n">
         <v>671.0169100391355</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>1.64</v>
+        <v>-1.45</v>
       </c>
       <c r="L5" t="n">
         <v>4</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.09</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44720.55208333334</v>
+        <v>44721.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>628.05</v>
+        <v>612.4</v>
       </c>
       <c r="I6" t="n">
         <v>625.3852896767174</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.04</v>
+        <v>-9.35</v>
       </c>
       <c r="L6" t="n">
-        <v>8.76</v>
+        <v>10.3</v>
       </c>
       <c r="M6" t="n">
         <v>0.2</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44727.38541666666</v>
+        <v>44727.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>624.75</v>
+        <v>628</v>
       </c>
       <c r="I7" t="n">
         <v>626.0508770804935</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.02</v>
+        <v>-2.55</v>
       </c>
       <c r="L7" t="n">
         <v>3.91</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>7.24</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44740.55208333334</v>
+        <v>44741.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>618.7</v>
+        <v>581.55</v>
       </c>
       <c r="I8" t="n">
         <v>583.7458785167887</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.48</v>
+        <v>-7.4</v>
       </c>
       <c r="L8" t="n">
-        <v>5.25</v>
+        <v>10.03</v>
       </c>
       <c r="M8" t="n">
-        <v>1.14</v>
+        <v>3.99</v>
       </c>
       <c r="N8" t="n">
-        <v>2.92</v>
+        <v>3.84</v>
       </c>
       <c r="O8" t="n">
         <v>3.63</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44762.55208333334</v>
+        <v>44763.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>575.25</v>
+        <v>591.1</v>
       </c>
       <c r="I9" t="n">
         <v>586.8508681099081</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
-        <v>1.08</v>
+        <v>-1.64</v>
       </c>
       <c r="L9" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="M9" t="n">
         <v>2.03</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.25</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44820.55208333334</v>
+        <v>44823.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>655.6</v>
+        <v>647.9</v>
       </c>
       <c r="I10" t="n">
         <v>650.9958544693258</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K10" t="n">
-        <v>10.91</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>3.57</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44851.55208333334</v>
+        <v>44852.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>617</v>
+        <v>624.05</v>
       </c>
       <c r="I11" t="n">
         <v>620.2856917812659</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K11" t="n">
-        <v>4.77</v>
+        <v>3.68</v>
       </c>
       <c r="L11" t="n">
         <v>4.67</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>6.34</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44854.55208333334</v>
+        <v>44855.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>593</v>
+        <v>585.4</v>
       </c>
       <c r="I12" t="n">
         <v>590.4971642740724</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.98</v>
+        <v>-6.19</v>
       </c>
       <c r="L12" t="n">
-        <v>6.23</v>
+        <v>6.9</v>
       </c>
       <c r="M12" t="n">
         <v>0.65</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>9.18</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44865.55208333334</v>
+        <v>44866.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>590</v>
+        <v>612.25</v>
       </c>
       <c r="I13" t="n">
         <v>608.2695320479557</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.79</v>
+        <v>-4.59</v>
       </c>
       <c r="L13" t="n">
-        <v>3.68</v>
+        <v>5.32</v>
       </c>
       <c r="M13" t="n">
         <v>2.52</v>
       </c>
       <c r="N13" t="n">
-        <v>2.56</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
         <v>-2.06</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.4</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44881.55208333334</v>
+        <v>44882.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>623.2</v>
+        <v>607.3</v>
       </c>
       <c r="I14" t="n">
         <v>611.4927830803865</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K14" t="n">
-        <v>1.79</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L14" t="n">
         <v>3.31</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>6.76</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44895.55208333334</v>
+        <v>44896.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>638.6</v>
+        <v>648.45</v>
       </c>
       <c r="I15" t="n">
         <v>642.7395510885435</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.15</v>
+        <v>-6.78</v>
       </c>
       <c r="L15" t="n">
-        <v>6.17</v>
+        <v>6.92</v>
       </c>
       <c r="M15" t="n">
         <v>0.62</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.36</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>665.3</v>
+        <v>647.65</v>
       </c>
       <c r="I16" t="n">
         <v>651.0804743628715</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6</v>
+        <v>-0.12</v>
       </c>
       <c r="L16" t="n">
         <v>2.76</v>
@@ -1353,7 +1544,7 @@
         <v>1.32</v>
       </c>
       <c r="N16" t="n">
-        <v>1.72</v>
+        <v>2.91</v>
       </c>
       <c r="O16" t="n">
         <v>-0.07000000000000001</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.04</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44964.38541666666</v>
+        <v>44964.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>633.8</v>
+        <v>650</v>
       </c>
       <c r="I17" t="n">
         <v>639.4535801072782</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>2.14</v>
+        <v>-0.36</v>
       </c>
       <c r="L17" t="n">
         <v>3.76</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>7.42</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44973.55208333334</v>
+        <v>44974.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>625.35</v>
+        <v>609.3</v>
       </c>
       <c r="I18" t="n">
         <v>616.3449618810714</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.79</v>
+        <v>-6.26</v>
       </c>
       <c r="L18" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
         <v>0.39</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>6.35</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>607.55</v>
+        <v>621.25</v>
       </c>
       <c r="I19" t="n">
         <v>620.2337661431669</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K19" t="n">
-        <v>0.29</v>
+        <v>-1.96</v>
       </c>
       <c r="L19" t="n">
         <v>2.74</v>
       </c>
       <c r="M19" t="n">
-        <v>0.82</v>
+        <v>1.43</v>
       </c>
       <c r="N19" t="n">
         <v>2.93</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>5.89</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>624.9</v>
+        <v>601.25</v>
       </c>
       <c r="I20" t="n">
         <v>604.8521365098984</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>0.59</v>
+        <v>-3.22</v>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>3.66</v>
       </c>
       <c r="M20" t="n">
         <v>1.28</v>
       </c>
       <c r="N20" t="n">
-        <v>0.91</v>
+        <v>4.62</v>
       </c>
       <c r="O20" t="n">
         <v>2.21</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>7.16</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45028.55208333334</v>
+        <v>45029.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>580.15</v>
+        <v>672.8</v>
       </c>
       <c r="I21" t="n">
         <v>590.3233635437522</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K21" t="n">
-        <v>3.51</v>
+        <v>-11.9</v>
       </c>
       <c r="L21" t="n">
-        <v>3.37</v>
+        <v>12.6</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>8.59</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>16.57</v>
       </c>
       <c r="O21" t="n">
         <v>-4.62</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>11.58</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45041.55208333334</v>
+        <v>45042.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>660</v>
+        <v>638.1</v>
       </c>
       <c r="I22" t="n">
         <v>640.7718020803459</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.9</v>
+        <v>-5.16</v>
       </c>
       <c r="L22" t="n">
         <v>6.36</v>
       </c>
       <c r="M22" t="n">
-        <v>0.92</v>
+        <v>1.52</v>
       </c>
       <c r="N22" t="n">
-        <v>2.06</v>
+        <v>2.43</v>
       </c>
       <c r="O22" t="n">
         <v>16.57</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>7.08</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45044.55208333334</v>
+        <v>45048.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>663</v>
+        <v>681.65</v>
       </c>
       <c r="I23" t="n">
         <v>679.9327386114062</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.9</v>
+        <v>-6.82</v>
       </c>
       <c r="L23" t="n">
-        <v>4.34</v>
+        <v>7.33</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
         <v>3.21</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>7.04</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45079.55208333334</v>
+        <v>45082.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>773</v>
+        <v>755.55</v>
       </c>
       <c r="I24" t="n">
         <v>758.125969358322</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K24" t="n">
-        <v>13.4</v>
+        <v>10.84</v>
       </c>
       <c r="L24" t="n">
         <v>2.58</v>
       </c>
       <c r="M24" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.34</v>
+        <v>2.86</v>
       </c>
       <c r="O24" t="n">
         <v>3.17</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>6.23</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45111.38541666666</v>
+        <v>45111.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>767</v>
+        <v>775.8</v>
       </c>
       <c r="I25" t="n">
         <v>773.0718370871033</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.52</v>
+        <v>-2.68</v>
       </c>
       <c r="L25" t="n">
         <v>3.77</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>4.55</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45128.55208333334</v>
+        <v>45131.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>765</v>
+        <v>738.4</v>
       </c>
       <c r="I26" t="n">
         <v>746.9812832460912</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.39</v>
+        <v>-4.82</v>
       </c>
       <c r="L26" t="n">
-        <v>3.26</v>
+        <v>6.36</v>
       </c>
       <c r="M26" t="n">
-        <v>0.52</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
         <v>3.58</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>5.22</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45160.55208333334</v>
+        <v>45161.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>728.15</v>
+        <v>735.7</v>
       </c>
       <c r="I27" t="n">
         <v>730.9259636673223</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K27" t="n">
-        <v>1.39</v>
+        <v>0.37</v>
       </c>
       <c r="L27" t="n">
         <v>0.93</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.91</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45197.38541666666</v>
+        <v>45197.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>721.5</v>
+        <v>718.85</v>
       </c>
       <c r="I28" t="n">
         <v>719.592759063951</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.93</v>
+        <v>-2.29</v>
       </c>
       <c r="L28" t="n">
         <v>3.83</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>5.48</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45240.55208333334</v>
+        <v>45242.76041666666</v>
       </c>
       <c r="H29" t="n">
-        <v>700</v>
+        <v>710.5</v>
       </c>
       <c r="I29" t="n">
         <v>702.3212825250514</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>43</v>
+        <v>45.20833333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>2.62</v>
+        <v>1.16</v>
       </c>
       <c r="L29" t="n">
         <v>1.59</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>4.95</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45307.55208333334</v>
+        <v>45308.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>773</v>
+        <v>755</v>
       </c>
       <c r="I30" t="n">
         <v>755.6231111922993</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>64.79166666666667</v>
+        <v>65.625</v>
       </c>
       <c r="K30" t="n">
-        <v>8.800000000000001</v>
+        <v>6.26</v>
       </c>
       <c r="L30" t="n">
         <v>0.99</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="N30" t="n">
         <v>3.24</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>7.4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45383.38541666666</v>
+        <v>45383.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>581.7</v>
+        <v>590.5</v>
       </c>
       <c r="I31" t="n">
         <v>584.0483095731349</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>75</v>
+        <v>75.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>22.95</v>
+        <v>21.79</v>
       </c>
       <c r="L31" t="n">
         <v>3.83</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.49</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45407.55208333334</v>
+        <v>45408.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>609.15</v>
+        <v>602.25</v>
       </c>
       <c r="I32" t="n">
         <v>607.0023240128386</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>3.16</v>
+        <v>1.99</v>
       </c>
       <c r="L32" t="n">
         <v>2.35</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>6.82</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45411.38541666666</v>
+        <v>45411.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>619.05</v>
+        <v>645</v>
       </c>
       <c r="I33" t="n">
         <v>634.9619405566683</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.79</v>
+        <v>-7.1</v>
       </c>
       <c r="L33" t="n">
-        <v>3.86</v>
+        <v>7.54</v>
       </c>
       <c r="M33" t="n">
         <v>4.09</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>8.57</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45434.38541666666</v>
+        <v>45434.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>607.4</v>
+        <v>604.75</v>
       </c>
       <c r="I34" t="n">
         <v>605.0629686872717</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.83</v>
+        <v>-6.24</v>
       </c>
       <c r="L34" t="n">
-        <v>6.31</v>
+        <v>6.89</v>
       </c>
       <c r="M34" t="n">
         <v>0.14</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>5.78</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45439.55208333334</v>
+        <v>45440.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>637</v>
+        <v>642.3</v>
       </c>
       <c r="I35" t="n">
         <v>639.6789474344362</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.33</v>
+        <v>-6.21</v>
       </c>
       <c r="L35" t="n">
-        <v>6.12</v>
+        <v>7.09</v>
       </c>
       <c r="M35" t="n">
         <v>0.61</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.43</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45478.55208333334</v>
+        <v>45481.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>672.25</v>
+        <v>644.6</v>
       </c>
       <c r="I36" t="n">
         <v>648.5706114729963</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K36" t="n">
-        <v>4.66</v>
+        <v>0.36</v>
       </c>
       <c r="L36" t="n">
         <v>5.67</v>
@@ -2493,7 +2924,7 @@
         <v>0.86</v>
       </c>
       <c r="N36" t="n">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="O36" t="n">
         <v>-0.13</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>7.97</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45497.38541666666</v>
+        <v>45497.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>652.6</v>
+        <v>660.7</v>
       </c>
       <c r="I37" t="n">
         <v>657.543235545889</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.24</v>
+        <v>-2.5</v>
       </c>
       <c r="L37" t="n">
         <v>3.67</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>5.61</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45513.55208333334</v>
+        <v>45516.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>626.4</v>
+        <v>609.3</v>
       </c>
       <c r="I38" t="n">
         <v>623.6585660974315</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.19</v>
+        <v>-7.78</v>
       </c>
       <c r="L38" t="n">
-        <v>6.08</v>
+        <v>8.41</v>
       </c>
       <c r="M38" t="n">
         <v>1.23</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.11</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45526.38541666666</v>
+        <v>45526.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>631.6</v>
+        <v>633.2</v>
       </c>
       <c r="I39" t="n">
         <v>632.0436140914918</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.66</v>
+        <v>-3.92</v>
       </c>
       <c r="L39" t="n">
         <v>4.6</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>4.04</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45574.38541666666</v>
+        <v>45574.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>718.8</v>
+        <v>707.15</v>
       </c>
       <c r="I40" t="n">
         <v>713.209594501385</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>47.83333333333334</v>
+        <v>48</v>
       </c>
       <c r="K40" t="n">
-        <v>13.52</v>
+        <v>11.68</v>
       </c>
       <c r="L40" t="n">
         <v>1.63</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>5.98</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45630.55208333334</v>
+        <v>45631.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>596.85</v>
+        <v>599</v>
       </c>
       <c r="I41" t="n">
         <v>598.5425732113403</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>56</v>
+        <v>56.83333333333334</v>
       </c>
       <c r="K41" t="n">
-        <v>15.6</v>
+        <v>15.29</v>
       </c>
       <c r="L41" t="n">
         <v>1.65</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.79</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45642.55208333334</v>
+        <v>45643.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>577</v>
+        <v>566.95</v>
       </c>
       <c r="I42" t="n">
         <v>572.9634536950015</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.67</v>
+        <v>-5.35</v>
       </c>
       <c r="L42" t="n">
-        <v>4.12</v>
+        <v>5.43</v>
       </c>
       <c r="M42" t="n">
         <v>0.48</v>
       </c>
       <c r="N42" t="n">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="O42" t="n">
         <v>0.34</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.44</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45658.38541666666</v>
+        <v>45658.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>558.35</v>
+        <v>570</v>
       </c>
       <c r="I43" t="n">
         <v>569.7149522620724</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>1.52</v>
+        <v>-0.54</v>
       </c>
       <c r="L43" t="n">
         <v>4.33</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>6.97</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>588</v>
+        <v>558.1</v>
       </c>
       <c r="I44" t="n">
         <v>575.3088520430234</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>3.16</v>
+        <v>-2.09</v>
       </c>
       <c r="L44" t="n">
-        <v>2.94</v>
+        <v>4.56</v>
       </c>
       <c r="M44" t="n">
-        <v>0.79</v>
+        <v>4.76</v>
       </c>
       <c r="N44" t="n">
         <v>4.49</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>9.41</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45713.55208333334</v>
+        <v>45715.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>524.2</v>
+        <v>553.35</v>
       </c>
       <c r="I45" t="n">
         <v>540.190258731112</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K45" t="n">
-        <v>6.07</v>
+        <v>0.85</v>
       </c>
       <c r="L45" t="n">
         <v>10.72</v>
       </c>
       <c r="M45" t="n">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="N45" t="n">
-        <v>4.42</v>
+        <v>6.1</v>
       </c>
       <c r="O45" t="n">
         <v>-4.1</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>9.41</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45726.55208333334</v>
+        <v>45727.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="I46" t="n">
         <v>523.5797069027532</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.95</v>
+        <v>-6.75</v>
       </c>
       <c r="L46" t="n">
-        <v>5.26</v>
+        <v>7.17</v>
       </c>
       <c r="M46" t="n">
         <v>1.37</v>
       </c>
       <c r="N46" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="O46" t="n">
         <v>6.1</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.98</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>506</v>
+        <v>526.5</v>
       </c>
       <c r="I47" t="n">
         <v>523.4918513078367</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>1.94</v>
+        <v>-2.03</v>
       </c>
       <c r="L47" t="n">
         <v>3.07</v>
@@ -3120,7 +3683,7 @@
         <v>0.76</v>
       </c>
       <c r="N47" t="n">
-        <v>2.84</v>
+        <v>3.84</v>
       </c>
       <c r="O47" t="n">
         <v>-2.38</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.26</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45744.38541666666</v>
+        <v>45744.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="I48" t="n">
         <v>537.2770893407127</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K48" t="n">
-        <v>3.32</v>
+        <v>1.04</v>
       </c>
       <c r="L48" t="n">
         <v>3.99</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>9.34</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>569.6</v>
+        <v>575.9</v>
       </c>
       <c r="I49" t="n">
         <v>570.4278408886823</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>18</v>
       </c>
       <c r="K49" t="n">
-        <v>-7.07</v>
+        <v>-8.25</v>
       </c>
       <c r="L49" t="n">
-        <v>7.31</v>
+        <v>8.85</v>
       </c>
       <c r="M49" t="n">
         <v>1.42</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.9</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45849.55208333334</v>
+        <v>45852.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>820.5</v>
+        <v>798.85</v>
       </c>
       <c r="I50" t="n">
         <v>800.2247112448539</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>87</v>
+        <v>89.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>42.47</v>
+        <v>38.71</v>
       </c>
       <c r="L50" t="n">
         <v>1.72</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.11</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>749.8</v>
+        <v>766.85</v>
       </c>
       <c r="I51" t="n">
         <v>764.2947204164877</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>35</v>
       </c>
       <c r="K51" t="n">
-        <v>6.14</v>
+        <v>4.01</v>
       </c>
       <c r="L51" t="n">
         <v>2.75</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>5.81</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45897.55208333334</v>
+        <v>45898.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>729.55</v>
+        <v>722.5</v>
       </c>
       <c r="I52" t="n">
         <v>725.5433846213366</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.86</v>
+        <v>-5.78</v>
       </c>
       <c r="L52" t="n">
-        <v>5.07</v>
+        <v>6.44</v>
       </c>
       <c r="M52" t="n">
-        <v>0.33</v>
+        <v>0.49</v>
       </c>
       <c r="N52" t="n">
         <v>1.82</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>4.88</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45922.55208333334</v>
+        <v>45923.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>708.4</v>
+        <v>728.8</v>
       </c>
       <c r="I53" t="n">
         <v>725.1186591243957</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K53" t="n">
-        <v>1.95</v>
+        <v>-0.87</v>
       </c>
       <c r="L53" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="M53" t="n">
         <v>0.68</v>
       </c>
       <c r="N53" t="n">
-        <v>2.29</v>
+        <v>3.44</v>
       </c>
       <c r="O53" t="n">
         <v>-1.51</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.45</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1009.3</v>
+        <v>973.4</v>
       </c>
       <c r="I54" t="n">
         <v>977.7242502556244</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>111.1666666666667</v>
+        <v>112</v>
       </c>
       <c r="K54" t="n">
-        <v>38.49</v>
+        <v>33.56</v>
       </c>
       <c r="L54" t="n">
         <v>2.73</v>
@@ -3519,7 +4166,7 @@
         <v>1.2</v>
       </c>
       <c r="N54" t="n">
-        <v>2.42</v>
+        <v>3.75</v>
       </c>
       <c r="O54" t="n">
         <v>3.44</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>6.34</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46038.38541666666</v>
+        <v>46038.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>1007.4</v>
+        <v>1023.35</v>
       </c>
       <c r="I55" t="n">
         <v>1010.074579967513</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.49</v>
+        <v>-5.13</v>
       </c>
       <c r="L55" t="n">
-        <v>4.02</v>
+        <v>5.81</v>
       </c>
       <c r="M55" t="n">
         <v>0.07000000000000001</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.86</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46045.38541666666</v>
+        <v>46045.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>980.2</v>
+        <v>967</v>
       </c>
       <c r="I56" t="n">
         <v>973.9053073724849</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.22</v>
+        <v>-5.51</v>
       </c>
       <c r="L56" t="n">
-        <v>5.38</v>
+        <v>6.06</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>7.02</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46071.38541666666</v>
+        <v>46071.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>1015.95</v>
+        <v>1023.5</v>
       </c>
       <c r="I57" t="n">
         <v>1021.527175801804</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.06</v>
+        <v>-5.84</v>
       </c>
       <c r="L57" t="n">
-        <v>5.78</v>
+        <v>5.9</v>
       </c>
       <c r="M57" t="n">
         <v>1.78</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>4.85</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46073.55208333334</v>
+        <v>46076.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1028.75</v>
+        <v>959.5</v>
       </c>
       <c r="I58" t="n">
         <v>982.7933595344676</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>0.51</v>
+        <v>-6.25</v>
       </c>
       <c r="L58" t="n">
-        <v>1.4</v>
+        <v>7.18</v>
       </c>
       <c r="M58" t="n">
-        <v>0.02</v>
+        <v>3.48</v>
       </c>
       <c r="N58" t="n">
-        <v>0.93</v>
+        <v>5.11</v>
       </c>
       <c r="O58" t="n">
         <v>2.27</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>8.25</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>887.4</v>
+        <v>960.15</v>
       </c>
       <c r="I59" t="n">
         <v>910.3770154789891</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K59" t="n">
-        <v>7.51</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L59" t="n">
         <v>5.25</v>
       </c>
       <c r="M59" t="n">
-        <v>2.14</v>
+        <v>3.67</v>
       </c>
       <c r="N59" t="n">
-        <v>3.83</v>
+        <v>9.26</v>
       </c>
       <c r="O59" t="n">
         <v>-5.11</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>10.93</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1022.5</v>
+        <v>1005</v>
       </c>
       <c r="I60" t="n">
         <v>1005.92479312747</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K60" t="n">
-        <v>6.49</v>
+        <v>4.67</v>
       </c>
       <c r="L60" t="n">
         <v>4.34</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>6.28</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46167.55208333334</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1004.5</v>
+        <v>1014.1</v>
       </c>
       <c r="I61" t="n">
         <v>1009.171614053762</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>0.05</v>
+        <v>-0.91</v>
       </c>
       <c r="L61" t="n">
         <v>1.73</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.74</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46175.55208333334</v>
+        <v>46176.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>977.4</v>
+        <v>960.15</v>
       </c>
       <c r="I62" t="n">
         <v>963.5625492035224</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.62</v>
+        <v>-5.32</v>
       </c>
       <c r="L62" t="n">
-        <v>6.2</v>
+        <v>7.17</v>
       </c>
       <c r="M62" t="n">
         <v>0.54</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>6.16</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46185.38541666666</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>964.7</v>
+        <v>1017.8</v>
       </c>
       <c r="I63" t="n">
         <v>1009.851751295934</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.47</v>
+        <v>-6</v>
       </c>
       <c r="L63" t="n">
-        <v>2.28</v>
+        <v>6.18</v>
       </c>
       <c r="M63" t="n">
         <v>0.49</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.77</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46220.55208333334</v>
+        <v>46223.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1032</v>
+        <v>994.6</v>
       </c>
       <c r="I64" t="n">
         <v>1019.617090267544</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>35</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K64" t="n">
-        <v>1.4</v>
+        <v>-2.28</v>
       </c>
       <c r="L64" t="n">
         <v>5.31</v>
@@ -4089,7 +4856,7 @@
         <v>1.22</v>
       </c>
       <c r="N64" t="n">
-        <v>3.18</v>
+        <v>3.69</v>
       </c>
       <c r="O64" t="n">
         <v>5.12</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>7.65</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46227.55208333334</v>
+        <v>46230.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1013.1</v>
+        <v>1056.3</v>
       </c>
       <c r="I65" t="n">
         <v>1020.729618616258</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.86</v>
+        <v>-6.2</v>
       </c>
       <c r="L65" t="n">
-        <v>4.42</v>
+        <v>6.78</v>
       </c>
       <c r="M65" t="n">
-        <v>0.39</v>
+        <v>0.78</v>
       </c>
       <c r="N65" t="n">
-        <v>3.29</v>
+        <v>4.14</v>
       </c>
       <c r="O65" t="n">
         <v>-3.69</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46261.55208333334</v>
+        <v>46262.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1089.6</v>
+        <v>1077.2</v>
       </c>
       <c r="I66" t="n">
         <v>1087.740778371586</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K66" t="n">
-        <v>3.15</v>
+        <v>1.98</v>
       </c>
       <c r="L66" t="n">
         <v>3.34</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,14 @@
       <c r="Q67" t="n">
         <v>80</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6365,7 +7176,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -6375,7 +7186,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.8</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="7">
@@ -6385,7 +7196,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>111.2</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
@@ -6395,7 +7206,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6405,7 +7216,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -6415,7 +7226,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="11">
@@ -6425,7 +7236,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -6435,7 +7246,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6445,7 +7256,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.2</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="14">
@@ -6455,7 +7266,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.66</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="15">
@@ -6465,7 +7276,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.89</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="16">
@@ -6475,7 +7286,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="17">
@@ -6485,7 +7296,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42.47</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="18">
@@ -6495,7 +7306,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.9</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="19">
@@ -6505,7 +7316,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.08</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="20">
@@ -6515,7 +7326,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.83</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="21">
@@ -6525,7 +7336,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.72</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="22">
@@ -6535,7 +7346,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -6545,7 +7356,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -6555,7 +7366,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="25">
@@ -6565,7 +7376,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.51</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="26">
@@ -6575,7 +7386,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.23</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="27">
@@ -6585,7 +7396,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.34</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="28">
@@ -6595,7 +7406,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
